--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run4/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8793,0.0923,0.0292,0.0017</t>
-  </si>
-  <si>
-    <t>0.9621,0.0099,0.0050,0.0079</t>
-  </si>
-  <si>
-    <t>0.9176,0.0931,0.0069,0.0007</t>
-  </si>
-  <si>
-    <t>0.8378,0.1287,0.0172,0.0083</t>
-  </si>
-  <si>
-    <t>0.9798,0.0313,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9689,0.0506,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9880,0.0168,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9856,0.0204,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9821,0.0262,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9648,0.0532,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9808,0.0301,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9854,0.0226,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.3839,0.5012,0.1109,0.0022</t>
-  </si>
-  <si>
-    <t>0.1794,0.0457,0.7938,0.0031</t>
-  </si>
-  <si>
-    <t>0.1713,0.0332,0.8051,0.0031</t>
-  </si>
-  <si>
-    <t>0.4049,0.0376,0.5715,0.0075</t>
-  </si>
-  <si>
-    <t>0.4450,0.3705,0.1273,0.0022</t>
-  </si>
-  <si>
-    <t>0.0274,0.9581,0.0396,0.0002</t>
-  </si>
-  <si>
-    <t>0.0594,0.9250,0.0367,0.0003</t>
-  </si>
-  <si>
-    <t>0.3054,0.7236,0.0201,0.0003</t>
-  </si>
-  <si>
-    <t>0.0909,0.8994,0.0303,0.0003</t>
-  </si>
-  <si>
-    <t>0.0287,0.9612,0.0238,0.0001</t>
-  </si>
-  <si>
-    <t>0.6671,0.0408,0.2805,0.0069</t>
-  </si>
-  <si>
-    <t>0.6136,0.0359,0.3790,0.0115</t>
-  </si>
-  <si>
-    <t>0.1205,0.0104,0.8923,0.0027</t>
-  </si>
-  <si>
-    <t>0.3282,0.0094,0.6945,0.0075</t>
-  </si>
-  <si>
-    <t>0.1340,0.0221,0.8566,0.0039</t>
-  </si>
-  <si>
-    <t>0.1989,0.0242,0.7802,0.0097</t>
-  </si>
-  <si>
-    <t>0.0040,0.0186,0.9910,0.0004</t>
-  </si>
-  <si>
-    <t>0.4197,0.5820,0.0282,0.0004</t>
-  </si>
-  <si>
-    <t>0.3942,0.5460,0.0642,0.0018</t>
-  </si>
-  <si>
-    <t>0.0013,0.0102,0.9972,0.0001</t>
-  </si>
-  <si>
-    <t>0.0293,0.8828,0.2793,0.0009</t>
-  </si>
-  <si>
-    <t>0.5053,0.5094,0.0368,0.0014</t>
-  </si>
-  <si>
-    <t>0.5726,0.4107,0.0357,0.0009</t>
-  </si>
-  <si>
-    <t>0.5099,0.5558,0.0136,0.0002</t>
-  </si>
-  <si>
-    <t>0.1359,0.8060,0.0770,0.0008</t>
-  </si>
-  <si>
-    <t>0.0744,0.5077,0.5823,0.0053</t>
-  </si>
-  <si>
-    <t>0.1286,0.0097,0.8772,0.0052</t>
-  </si>
-  <si>
-    <t>0.0916,0.0178,0.8963,0.0054</t>
-  </si>
-  <si>
-    <t>0.2347,0.0168,0.7701,0.0062</t>
-  </si>
-  <si>
-    <t>0.0463,0.0935,0.9088,0.0023</t>
-  </si>
-  <si>
-    <t>0.0064,0.9655,0.1210,0.0002</t>
-  </si>
-  <si>
-    <t>0.0293,0.0119,0.9593,0.0019</t>
-  </si>
-  <si>
-    <t>0.5209,0.4118,0.0778,0.0153</t>
-  </si>
-  <si>
-    <t>0.0101,0.9836,0.0140,0.0000</t>
-  </si>
-  <si>
-    <t>0.0112,0.9770,0.0412,0.0001</t>
-  </si>
-  <si>
-    <t>0.0025,0.9940,0.0161,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.5969,0.9562,0.0007</t>
-  </si>
-  <si>
-    <t>0.0022,0.0575,0.9930,0.0003</t>
-  </si>
-  <si>
-    <t>0.0237,0.0142,0.9681,0.0014</t>
-  </si>
-  <si>
-    <t>0.0352,0.0070,0.9608,0.0008</t>
-  </si>
-  <si>
-    <t>0.0044,0.0542,0.9856,0.0003</t>
-  </si>
-  <si>
-    <t>0.0191,0.0082,0.9723,0.0015</t>
-  </si>
-  <si>
-    <t>0.9499,0.0801,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9506,0.0788,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.8952,0.1494,0.0045,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.2558,0.9812,0.0003</t>
-  </si>
-  <si>
-    <t>0.9449,0.0813,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9716,0.0428,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9088,0.1398,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0014,0.9195,0.8597,0.0002</t>
-  </si>
-  <si>
-    <t>0.0150,0.1077,0.9611,0.0021</t>
-  </si>
-  <si>
-    <t>0.0497,0.0120,0.9404,0.0029</t>
-  </si>
-  <si>
-    <t>0.0006,0.7498,0.9757,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0054,0.9937,0.0008</t>
-  </si>
-  <si>
-    <t>0.0540,0.9221,0.0397,0.0002</t>
-  </si>
-  <si>
-    <t>0.0024,0.9950,0.0050,0.0000</t>
-  </si>
-  <si>
-    <t>0.4112,0.1265,0.4252,0.0045</t>
-  </si>
-  <si>
-    <t>0.3343,0.5747,0.0840,0.0015</t>
-  </si>
-  <si>
-    <t>0.0005,0.1123,0.9965,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.8799,0.9312,0.0002</t>
-  </si>
-  <si>
-    <t>0.0219,0.7071,0.7495,0.0014</t>
-  </si>
-  <si>
-    <t>0.0070,0.9373,0.3862,0.0010</t>
-  </si>
-  <si>
-    <t>0.0009,0.9598,0.7503,0.0001</t>
-  </si>
-  <si>
-    <t>0.6859,0.0060,0.1550,0.0793</t>
-  </si>
-  <si>
-    <t>0.8512,0.0061,0.0049,0.0696</t>
-  </si>
-  <si>
-    <t>0.4764,0.0028,0.0084,0.4904</t>
-  </si>
-  <si>
-    <t>0.6967,0.0239,0.0290,0.1282</t>
-  </si>
-  <si>
-    <t>0.6930,0.0219,0.0265,0.1360</t>
-  </si>
-  <si>
-    <t>0.5081,0.0051,0.0267,0.3762</t>
-  </si>
-  <si>
-    <t>0.0008,0.9087,0.9198,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.8655,0.9809,0.0001</t>
-  </si>
-  <si>
-    <t>0.0105,0.7722,0.8007,0.0012</t>
-  </si>
-  <si>
-    <t>0.0013,0.4021,0.9847,0.0009</t>
-  </si>
-  <si>
-    <t>0.0051,0.5981,0.9353,0.0005</t>
-  </si>
-  <si>
-    <t>0.0052,0.5743,0.9350,0.0005</t>
-  </si>
-  <si>
-    <t>0.9797,0.0321,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9764,0.0353,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9204,0.1219,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.9609,0.0615,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9723,0.0427,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9488,0.0831,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9623,0.0577,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9828,0.0257,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9958,0.0060,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9668,0.0522,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9932,0.0094,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9781,0.0334,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9819,0.0280,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9787,0.0319,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9786,0.0315,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9855,0.0221,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0131,0.0044,0.9820,0.0005</t>
-  </si>
-  <si>
-    <t>0.2403,0.0784,0.6812,0.0055</t>
-  </si>
-  <si>
-    <t>0.6858,0.0825,0.1923,0.0057</t>
-  </si>
-  <si>
-    <t>0.0953,0.0121,0.9015,0.0030</t>
-  </si>
-  <si>
-    <t>0.1838,0.8577,0.0059,0.0001</t>
-  </si>
-  <si>
-    <t>0.1652,0.8658,0.0068,0.0000</t>
-  </si>
-  <si>
-    <t>0.2695,0.7456,0.0285,0.0005</t>
-  </si>
-  <si>
-    <t>0.2644,0.7595,0.0180,0.0003</t>
-  </si>
-  <si>
-    <t>0.0990,0.8982,0.0185,0.0001</t>
-  </si>
-  <si>
-    <t>0.0619,0.9453,0.0052,0.0000</t>
-  </si>
-  <si>
-    <t>0.5885,0.4489,0.0214,0.0005</t>
-  </si>
-  <si>
-    <t>0.4327,0.1517,0.3592,0.0046</t>
-  </si>
-  <si>
-    <t>0.3909,0.0288,0.6099,0.0059</t>
-  </si>
-  <si>
-    <t>0.2958,0.6418,0.0512,0.0008</t>
-  </si>
-  <si>
-    <t>0.4828,0.1782,0.2318,0.0038</t>
-  </si>
-  <si>
-    <t>0.6744,0.0584,0.2489,0.0297</t>
-  </si>
-  <si>
-    <t>0.0016,0.9954,0.0182,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.9958,0.0078,0.0000</t>
-  </si>
-  <si>
-    <t>0.0273,0.9573,0.0320,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9880,0.6159,0.0000</t>
-  </si>
-  <si>
-    <t>0.1333,0.8536,0.0318,0.0003</t>
-  </si>
-  <si>
-    <t>0.3370,0.6750,0.0273,0.0005</t>
-  </si>
-  <si>
-    <t>0.5176,0.5260,0.0192,0.0004</t>
-  </si>
-  <si>
-    <t>0.9227,0.1122,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.9846,0.0213,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9849,0.0223,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9420,0.0797,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9901,0.0129,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9175,0.1234,0.0026,0.0001</t>
-  </si>
-  <si>
-    <t>0.9758,0.0364,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9689,0.0463,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.5509,0.9607,0.0005</t>
-  </si>
-  <si>
-    <t>0.0057,0.3856,0.9599,0.0004</t>
-  </si>
-  <si>
-    <t>0.0190,0.0464,0.9663,0.0010</t>
-  </si>
-  <si>
-    <t>0.0500,0.1046,0.8885,0.0026</t>
-  </si>
-  <si>
-    <t>0.6807,0.1275,0.1357,0.0048</t>
-  </si>
-  <si>
-    <t>0.6184,0.2273,0.1004,0.0019</t>
-  </si>
-  <si>
-    <t>0.4654,0.0268,0.5438,0.0075</t>
-  </si>
-  <si>
-    <t>0.4379,0.4988,0.0576,0.0014</t>
-  </si>
-  <si>
-    <t>0.8565,0.0288,0.0358,0.0256</t>
-  </si>
-  <si>
-    <t>0.0175,0.0013,0.0025,0.9903</t>
-  </si>
-  <si>
-    <t>0.1813,0.0483,0.0222,0.7649</t>
-  </si>
-  <si>
-    <t>0.9166,0.0254,0.0144,0.0140</t>
-  </si>
-  <si>
-    <t>0.0003,0.9798,0.7766,0.0000</t>
-  </si>
-  <si>
-    <t>0.9823,0.0241,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.3118,0.7378,0.0087,0.0001</t>
-  </si>
-  <si>
-    <t>0.9738,0.0346,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.4204,0.6447,0.0100,0.0002</t>
-  </si>
-  <si>
-    <t>0.9635,0.0468,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.9066,0.0964,0.0093,0.0013</t>
-  </si>
-  <si>
-    <t>0.9697,0.0470,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.3155,0.0450,0.6390,0.0224</t>
-  </si>
-  <si>
-    <t>0.9511,0.0500,0.0056,0.0007</t>
-  </si>
-  <si>
-    <t>0.7384,0.3220,0.0133,0.0004</t>
-  </si>
-  <si>
-    <t>0.4445,0.5985,0.0160,0.0003</t>
-  </si>
-  <si>
-    <t>0.6099,0.4226,0.0245,0.0007</t>
-  </si>
-  <si>
-    <t>0.6684,0.3645,0.0236,0.0007</t>
-  </si>
-  <si>
-    <t>0.1830,0.8035,0.0353,0.0005</t>
-  </si>
-  <si>
-    <t>0.2702,0.5694,0.1484,0.0016</t>
-  </si>
-  <si>
-    <t>0.4683,0.5473,0.0271,0.0006</t>
-  </si>
-  <si>
-    <t>0.9561,0.0651,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9752,0.0368,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9803,0.0274,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0139,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9262,0.1058,0.0034,0.0002</t>
-  </si>
-  <si>
-    <t>0.9691,0.0494,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9880,0.0171,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9816,0.0253,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.3172,0.7151,0.0177,0.0003</t>
-  </si>
-  <si>
-    <t>0.6236,0.4583,0.0075,0.0002</t>
-  </si>
-  <si>
-    <t>0.6354,0.4529,0.0073,0.0001</t>
-  </si>
-  <si>
-    <t>0.4711,0.4420,0.0916,0.0016</t>
-  </si>
-  <si>
-    <t>0.7322,0.3555,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.8522,0.2096,0.0053,0.0002</t>
-  </si>
-  <si>
-    <t>0.9371,0.0911,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.7915,0.2796,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0925,0.9963,0.0001</t>
-  </si>
-  <si>
-    <t>0.7531,0.3162,0.0092,0.0003</t>
-  </si>
-  <si>
-    <t>0.0063,0.0632,0.9843,0.0004</t>
-  </si>
-  <si>
-    <t>0.0196,0.1136,0.9548,0.0013</t>
-  </si>
-  <si>
-    <t>0.0963,0.0321,0.8835,0.0025</t>
-  </si>
-  <si>
-    <t>0.0203,0.4352,0.8713,0.0012</t>
-  </si>
-  <si>
-    <t>0.0169,0.2246,0.9384,0.0010</t>
-  </si>
-  <si>
-    <t>0.0034,0.0049,0.9941,0.0004</t>
-  </si>
-  <si>
-    <t>0.0038,0.0435,0.9903,0.0003</t>
-  </si>
-  <si>
-    <t>0.3625,0.2523,0.3663,0.0062</t>
-  </si>
-  <si>
-    <t>0.5006,0.2568,0.1718,0.0034</t>
-  </si>
-  <si>
-    <t>0.3047,0.1521,0.5077,0.0039</t>
-  </si>
-  <si>
-    <t>0.2365,0.3672,0.3510,0.0034</t>
-  </si>
-  <si>
-    <t>0.3135,0.2777,0.3522,0.0044</t>
-  </si>
-  <si>
-    <t>0.3177,0.2205,0.3889,0.0029</t>
-  </si>
-  <si>
-    <t>0.4678,0.2568,0.1870,0.0028</t>
-  </si>
-  <si>
-    <t>0.3458,0.5308,0.1009,0.0016</t>
-  </si>
-  <si>
-    <t>0.3237,0.7043,0.0195,0.0003</t>
-  </si>
-  <si>
-    <t>0.4744,0.5899,0.0153,0.0004</t>
-  </si>
-  <si>
-    <t>0.4490,0.6026,0.0160,0.0003</t>
-  </si>
-  <si>
-    <t>0.8231,0.2644,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.6939,0.4149,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.3612,0.5713,0.0580,0.0009</t>
-  </si>
-  <si>
-    <t>0.5326,0.0251,0.4799,0.0044</t>
-  </si>
-  <si>
-    <t>0.7465,0.0647,0.1603,0.0040</t>
-  </si>
-  <si>
-    <t>0.4589,0.0804,0.4226,0.0068</t>
-  </si>
-  <si>
-    <t>0.6823,0.2252,0.0649,0.0013</t>
-  </si>
-  <si>
-    <t>0.0202,0.0263,0.9663,0.0010</t>
-  </si>
-  <si>
-    <t>0.0253,0.0252,0.9589,0.0027</t>
-  </si>
-  <si>
-    <t>0.0332,0.0741,0.9378,0.0033</t>
-  </si>
-  <si>
-    <t>0.5157,0.0158,0.5212,0.0103</t>
-  </si>
-  <si>
-    <t>0.0629,0.0652,0.8889,0.0060</t>
-  </si>
-  <si>
-    <t>0.9790,0.0323,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9747,0.0368,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9401,0.0914,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.9384,0.0991,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.8686,0.1956,0.0039,0.0002</t>
-  </si>
-  <si>
-    <t>0.9101,0.1282,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9849,0.0227,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9596,0.0586,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0524,0.0979,0.9005,0.0023</t>
-  </si>
-  <si>
-    <t>0.3774,0.6311,0.0287,0.0009</t>
-  </si>
-  <si>
-    <t>0.8327,0.1751,0.0186,0.0008</t>
-  </si>
-  <si>
-    <t>0.0049,0.0149,0.9913,0.0006</t>
-  </si>
-  <si>
-    <t>0.0020,0.0747,0.9921,0.0004</t>
-  </si>
-  <si>
-    <t>0.0157,0.1516,0.9450,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0123,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.1429,0.0093,0.8590,0.0042</t>
-  </si>
-  <si>
-    <t>0.0007,0.0101,0.9980,0.0002</t>
-  </si>
-  <si>
-    <t>0.0264,0.0241,0.9605,0.0017</t>
-  </si>
-  <si>
-    <t>0.0410,0.3192,0.8499,0.0019</t>
-  </si>
-  <si>
-    <t>0.5502,0.1473,0.2116,0.0042</t>
-  </si>
-  <si>
-    <t>0.7575,0.0511,0.1814,0.0053</t>
-  </si>
-  <si>
-    <t>0.4896,0.4008,0.0752,0.0012</t>
-  </si>
-  <si>
-    <t>0.9634,0.0599,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9707,0.0429,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.9669,0.0499,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9707,0.0417,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9816,0.0287,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.8334,0.2402,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.9798,0.0323,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9767,0.0385,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.3327,0.0405,0.6194,0.0092</t>
-  </si>
-  <si>
-    <t>0.0107,0.0932,0.9697,0.0008</t>
-  </si>
-  <si>
-    <t>0.0108,0.1250,0.9614,0.0008</t>
-  </si>
-  <si>
-    <t>0.1865,0.2876,0.5200,0.0029</t>
-  </si>
-  <si>
-    <t>0.0097,0.0102,0.9835,0.0007</t>
-  </si>
-  <si>
-    <t>0.5214,0.0549,0.4233,0.0144</t>
-  </si>
-  <si>
-    <t>0.3627,0.0622,0.5703,0.0102</t>
-  </si>
-  <si>
-    <t>0.0849,0.0040,0.9120,0.0073</t>
-  </si>
-  <si>
-    <t>0.9594,0.0427,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.7333,0.0198,0.0357,0.1083</t>
-  </si>
-  <si>
-    <t>0.9794,0.0078,0.0032,0.0029</t>
-  </si>
-  <si>
-    <t>0.6868,0.0078,0.0090,0.1941</t>
-  </si>
-  <si>
-    <t>0.8790,0.0338,0.0150,0.0254</t>
-  </si>
-  <si>
-    <t>0.7580,0.1648,0.0699,0.0044</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.6801,0.2465,0.0728,0.0025</t>
+  </si>
+  <si>
+    <t>0.9628,0.0089,0.0056,0.0075</t>
+  </si>
+  <si>
+    <t>0.8821,0.1449,0.0061,0.0005</t>
+  </si>
+  <si>
+    <t>0.8610,0.1281,0.0151,0.0030</t>
+  </si>
+  <si>
+    <t>0.9895,0.0156,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9701,0.0481,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9772,0.0327,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9868,0.0179,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9749,0.0363,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9784,0.0320,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9767,0.0326,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9905,0.0137,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.7278,0.1810,0.0781,0.0022</t>
+  </si>
+  <si>
+    <t>0.3048,0.0668,0.6241,0.0040</t>
+  </si>
+  <si>
+    <t>0.3706,0.0618,0.5502,0.0045</t>
+  </si>
+  <si>
+    <t>0.0521,0.0716,0.9071,0.0024</t>
+  </si>
+  <si>
+    <t>0.4442,0.4316,0.1113,0.0034</t>
+  </si>
+  <si>
+    <t>0.0204,0.9688,0.0292,0.0001</t>
+  </si>
+  <si>
+    <t>0.0617,0.9193,0.0446,0.0004</t>
+  </si>
+  <si>
+    <t>0.1970,0.8159,0.0205,0.0002</t>
+  </si>
+  <si>
+    <t>0.0802,0.9092,0.0319,0.0003</t>
+  </si>
+  <si>
+    <t>0.0394,0.9457,0.0367,0.0002</t>
+  </si>
+  <si>
+    <t>0.6124,0.0317,0.3530,0.0085</t>
+  </si>
+  <si>
+    <t>0.6907,0.0134,0.3273,0.0128</t>
+  </si>
+  <si>
+    <t>0.3501,0.0222,0.6755,0.0066</t>
+  </si>
+  <si>
+    <t>0.4825,0.0228,0.5210,0.0100</t>
+  </si>
+  <si>
+    <t>0.3256,0.0113,0.7064,0.0060</t>
+  </si>
+  <si>
+    <t>0.3250,0.0299,0.6681,0.0095</t>
+  </si>
+  <si>
+    <t>0.0092,0.0070,0.9857,0.0009</t>
+  </si>
+  <si>
+    <t>0.2329,0.7575,0.0332,0.0005</t>
+  </si>
+  <si>
+    <t>0.5287,0.2820,0.1216,0.0021</t>
+  </si>
+  <si>
+    <t>0.0029,0.0110,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.0324,0.6740,0.6833,0.0014</t>
+  </si>
+  <si>
+    <t>0.5160,0.4814,0.0374,0.0009</t>
+  </si>
+  <si>
+    <t>0.4470,0.5480,0.0326,0.0006</t>
+  </si>
+  <si>
+    <t>0.5951,0.4738,0.0143,0.0003</t>
+  </si>
+  <si>
+    <t>0.1520,0.7640,0.1070,0.0011</t>
+  </si>
+  <si>
+    <t>0.0681,0.5875,0.5336,0.0075</t>
+  </si>
+  <si>
+    <t>0.0593,0.0109,0.9320,0.0027</t>
+  </si>
+  <si>
+    <t>0.1891,0.0180,0.8095,0.0100</t>
+  </si>
+  <si>
+    <t>0.0918,0.0099,0.9083,0.0032</t>
+  </si>
+  <si>
+    <t>0.0323,0.1737,0.9060,0.0017</t>
+  </si>
+  <si>
+    <t>0.0021,0.9829,0.1238,0.0001</t>
+  </si>
+  <si>
+    <t>0.0230,0.0352,0.9584,0.0017</t>
+  </si>
+  <si>
+    <t>0.4953,0.3692,0.1253,0.0131</t>
+  </si>
+  <si>
+    <t>0.0113,0.9798,0.0249,0.0001</t>
+  </si>
+  <si>
+    <t>0.0075,0.9834,0.0381,0.0001</t>
+  </si>
+  <si>
+    <t>0.0050,0.9894,0.0213,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.4962,0.9617,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.5792,0.9944,0.0000</t>
+  </si>
+  <si>
+    <t>0.1276,0.0203,0.8656,0.0056</t>
+  </si>
+  <si>
+    <t>0.0226,0.0055,0.9714,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.0098,0.9965,0.0001</t>
+  </si>
+  <si>
+    <t>0.0276,0.0162,0.9564,0.0024</t>
+  </si>
+  <si>
+    <t>0.8608,0.2149,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9135,0.1366,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9483,0.0810,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0056,0.2228,0.9744,0.0004</t>
+  </si>
+  <si>
+    <t>0.9718,0.0417,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9568,0.0676,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9666,0.0544,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0039,0.8101,0.8572,0.0006</t>
+  </si>
+  <si>
+    <t>0.0068,0.1476,0.9749,0.0005</t>
+  </si>
+  <si>
+    <t>0.0562,0.0190,0.9283,0.0033</t>
+  </si>
+  <si>
+    <t>0.0001,0.8873,0.9844,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.0071,0.9933,0.0005</t>
+  </si>
+  <si>
+    <t>0.0268,0.9565,0.0302,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.9957,0.0039,0.0000</t>
+  </si>
+  <si>
+    <t>0.5700,0.2005,0.1648,0.0024</t>
+  </si>
+  <si>
+    <t>0.2742,0.4893,0.2200,0.0026</t>
+  </si>
+  <si>
+    <t>0.0011,0.0549,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.8367,0.9645,0.0001</t>
+  </si>
+  <si>
+    <t>0.0097,0.7030,0.8534,0.0008</t>
+  </si>
+  <si>
+    <t>0.0058,0.9382,0.4125,0.0008</t>
+  </si>
+  <si>
+    <t>0.0015,0.9465,0.6854,0.0002</t>
+  </si>
+  <si>
+    <t>0.5745,0.0038,0.0394,0.2585</t>
+  </si>
+  <si>
+    <t>0.1179,0.0018,0.0019,0.9288</t>
+  </si>
+  <si>
+    <t>0.3359,0.0036,0.0060,0.6714</t>
+  </si>
+  <si>
+    <t>0.4664,0.0119,0.0261,0.3920</t>
+  </si>
+  <si>
+    <t>0.7761,0.0071,0.0084,0.1149</t>
+  </si>
+  <si>
+    <t>0.3608,0.0029,0.0103,0.6448</t>
+  </si>
+  <si>
+    <t>0.0025,0.9154,0.8121,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.3777,0.9963,0.0001</t>
+  </si>
+  <si>
+    <t>0.0109,0.7591,0.8163,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.7437,0.9787,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.5343,0.9609,0.0004</t>
+  </si>
+  <si>
+    <t>0.0015,0.7700,0.9505,0.0002</t>
+  </si>
+  <si>
+    <t>0.9425,0.0905,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9558,0.0707,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9729,0.0420,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9567,0.0678,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9728,0.0430,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9889,0.0165,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9542,0.0689,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9707,0.0457,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9804,0.0319,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9734,0.0409,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0097,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9770,0.0354,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9846,0.0237,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9539,0.0731,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9816,0.0290,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9895,0.0144,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.0015,0.9960,0.0002</t>
+  </si>
+  <si>
+    <t>0.0584,0.0406,0.9164,0.0026</t>
+  </si>
+  <si>
+    <t>0.6966,0.0951,0.1784,0.0061</t>
+  </si>
+  <si>
+    <t>0.5106,0.0159,0.5233,0.0059</t>
+  </si>
+  <si>
+    <t>0.1288,0.8832,0.0122,0.0001</t>
+  </si>
+  <si>
+    <t>0.1255,0.8888,0.0101,0.0001</t>
+  </si>
+  <si>
+    <t>0.1634,0.8542,0.0156,0.0002</t>
+  </si>
+  <si>
+    <t>0.2644,0.7609,0.0159,0.0003</t>
+  </si>
+  <si>
+    <t>0.1329,0.8726,0.0179,0.0002</t>
+  </si>
+  <si>
+    <t>0.0420,0.9588,0.0067,0.0000</t>
+  </si>
+  <si>
+    <t>0.5597,0.4799,0.0175,0.0004</t>
+  </si>
+  <si>
+    <t>0.6364,0.3260,0.0558,0.0016</t>
+  </si>
+  <si>
+    <t>0.2794,0.0253,0.7233,0.0050</t>
+  </si>
+  <si>
+    <t>0.5406,0.2967,0.1050,0.0028</t>
+  </si>
+  <si>
+    <t>0.5328,0.1971,0.1781,0.0038</t>
+  </si>
+  <si>
+    <t>0.7429,0.0579,0.1527,0.0318</t>
+  </si>
+  <si>
+    <t>0.0038,0.9912,0.0221,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9938,0.0130,0.0000</t>
+  </si>
+  <si>
+    <t>0.0289,0.9532,0.0433,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9827,0.8175,0.0000</t>
+  </si>
+  <si>
+    <t>0.1283,0.8408,0.0460,0.0004</t>
+  </si>
+  <si>
+    <t>0.3236,0.6514,0.0363,0.0005</t>
+  </si>
+  <si>
+    <t>0.5821,0.4588,0.0225,0.0005</t>
+  </si>
+  <si>
+    <t>0.8965,0.1527,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0099,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9206,0.1169,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.9628,0.0511,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.9938,0.0086,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9605,0.0600,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9699,0.0484,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9907,0.0131,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0438,0.3259,0.8364,0.0038</t>
+  </si>
+  <si>
+    <t>0.0091,0.5090,0.9242,0.0006</t>
+  </si>
+  <si>
+    <t>0.0289,0.0326,0.9598,0.0012</t>
+  </si>
+  <si>
+    <t>0.0252,0.0771,0.9456,0.0018</t>
+  </si>
+  <si>
+    <t>0.7273,0.0635,0.1697,0.0039</t>
+  </si>
+  <si>
+    <t>0.6683,0.2827,0.0515,0.0012</t>
+  </si>
+  <si>
+    <t>0.4082,0.0219,0.6167,0.0049</t>
+  </si>
+  <si>
+    <t>0.4639,0.4518,0.0634,0.0016</t>
+  </si>
+  <si>
+    <t>0.8527,0.0179,0.0220,0.0385</t>
+  </si>
+  <si>
+    <t>0.0136,0.0017,0.0025,0.9923</t>
+  </si>
+  <si>
+    <t>0.2927,0.0462,0.0534,0.5987</t>
+  </si>
+  <si>
+    <t>0.7714,0.0129,0.0122,0.0983</t>
+  </si>
+  <si>
+    <t>0.0005,0.9567,0.8478,0.0001</t>
+  </si>
+  <si>
+    <t>0.9827,0.0243,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.3594,0.7097,0.0064,0.0001</t>
+  </si>
+  <si>
+    <t>0.9481,0.0707,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.4670,0.5934,0.0114,0.0002</t>
+  </si>
+  <si>
+    <t>0.9736,0.0334,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9432,0.0465,0.0094,0.0016</t>
+  </si>
+  <si>
+    <t>0.9647,0.0544,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.3988,0.0562,0.5295,0.0202</t>
+  </si>
+  <si>
+    <t>0.8438,0.1621,0.0173,0.0014</t>
+  </si>
+  <si>
+    <t>0.8416,0.2188,0.0067,0.0003</t>
+  </si>
+  <si>
+    <t>0.2353,0.7712,0.0222,0.0003</t>
+  </si>
+  <si>
+    <t>0.6582,0.3991,0.0180,0.0005</t>
+  </si>
+  <si>
+    <t>0.4961,0.4862,0.0424,0.0009</t>
+  </si>
+  <si>
+    <t>0.1916,0.8072,0.0252,0.0004</t>
+  </si>
+  <si>
+    <t>0.5501,0.4270,0.0419,0.0008</t>
+  </si>
+  <si>
+    <t>0.3878,0.5681,0.0580,0.0013</t>
+  </si>
+  <si>
+    <t>0.9678,0.0485,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9636,0.0548,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9862,0.0193,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9527,0.0662,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.9756,0.0349,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9669,0.0490,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9515,0.0760,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9474,0.0751,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.4269,0.6209,0.0173,0.0003</t>
+  </si>
+  <si>
+    <t>0.7734,0.3085,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.3641,0.6830,0.0122,0.0002</t>
+  </si>
+  <si>
+    <t>0.4730,0.5186,0.0380,0.0007</t>
+  </si>
+  <si>
+    <t>0.6814,0.4111,0.0071,0.0002</t>
+  </si>
+  <si>
+    <t>0.8852,0.1587,0.0057,0.0002</t>
+  </si>
+  <si>
+    <t>0.8224,0.2504,0.0061,0.0002</t>
+  </si>
+  <si>
+    <t>0.9291,0.0990,0.0035,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0660,0.9954,0.0002</t>
+  </si>
+  <si>
+    <t>0.7575,0.3150,0.0087,0.0002</t>
+  </si>
+  <si>
+    <t>0.0062,0.0380,0.9866,0.0004</t>
+  </si>
+  <si>
+    <t>0.0240,0.1271,0.9438,0.0015</t>
+  </si>
+  <si>
+    <t>0.2329,0.0347,0.7372,0.0066</t>
+  </si>
+  <si>
+    <t>0.0637,0.1534,0.8593,0.0028</t>
+  </si>
+  <si>
+    <t>0.0367,0.1160,0.9253,0.0014</t>
+  </si>
+  <si>
+    <t>0.0110,0.0041,0.9855,0.0006</t>
+  </si>
+  <si>
+    <t>0.0071,0.0399,0.9843,0.0004</t>
+  </si>
+  <si>
+    <t>0.2349,0.1971,0.5705,0.0047</t>
+  </si>
+  <si>
+    <t>0.2680,0.0689,0.6493,0.0033</t>
+  </si>
+  <si>
+    <t>0.1988,0.4017,0.4090,0.0028</t>
+  </si>
+  <si>
+    <t>0.2631,0.3045,0.3777,0.0037</t>
+  </si>
+  <si>
+    <t>0.1812,0.5096,0.3199,0.0027</t>
+  </si>
+  <si>
+    <t>0.3855,0.5400,0.0619,0.0010</t>
+  </si>
+  <si>
+    <t>0.5465,0.2324,0.1340,0.0025</t>
+  </si>
+  <si>
+    <t>0.3347,0.4126,0.2301,0.0039</t>
+  </si>
+  <si>
+    <t>0.4325,0.6232,0.0142,0.0002</t>
+  </si>
+  <si>
+    <t>0.3866,0.6498,0.0199,0.0003</t>
+  </si>
+  <si>
+    <t>0.5439,0.5251,0.0139,0.0003</t>
+  </si>
+  <si>
+    <t>0.8047,0.2785,0.0053,0.0002</t>
+  </si>
+  <si>
+    <t>0.5868,0.5106,0.0072,0.0002</t>
+  </si>
+  <si>
+    <t>0.4112,0.4855,0.0852,0.0015</t>
+  </si>
+  <si>
+    <t>0.5829,0.1086,0.2472,0.0045</t>
+  </si>
+  <si>
+    <t>0.6899,0.1947,0.0778,0.0030</t>
+  </si>
+  <si>
+    <t>0.5219,0.0457,0.4323,0.0066</t>
+  </si>
+  <si>
+    <t>0.8013,0.0802,0.1028,0.0030</t>
+  </si>
+  <si>
+    <t>0.0098,0.0230,0.9818,0.0006</t>
+  </si>
+  <si>
+    <t>0.1994,0.0192,0.7864,0.0151</t>
+  </si>
+  <si>
+    <t>0.0755,0.0744,0.8811,0.0055</t>
+  </si>
+  <si>
+    <t>0.0748,0.0086,0.9253,0.0031</t>
+  </si>
+  <si>
+    <t>0.0845,0.0191,0.9023,0.0031</t>
+  </si>
+  <si>
+    <t>0.9752,0.0389,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9590,0.0577,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.9321,0.1034,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.9601,0.0606,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9092,0.1354,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.9570,0.0655,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9763,0.0355,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9584,0.0607,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0483,0.2463,0.8533,0.0021</t>
+  </si>
+  <si>
+    <t>0.3328,0.6428,0.0480,0.0014</t>
+  </si>
+  <si>
+    <t>0.9429,0.0552,0.0084,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0051,0.9964,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0185,0.9979,0.0003</t>
+  </si>
+  <si>
+    <t>0.0100,0.4653,0.9217,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0084,0.9989,0.0002</t>
+  </si>
+  <si>
+    <t>0.2180,0.0389,0.7307,0.0074</t>
+  </si>
+  <si>
+    <t>0.0025,0.0084,0.9950,0.0002</t>
+  </si>
+  <si>
+    <t>0.0626,0.0337,0.9036,0.0040</t>
+  </si>
+  <si>
+    <t>0.0275,0.3947,0.8561,0.0018</t>
+  </si>
+  <si>
+    <t>0.6251,0.0688,0.2825,0.0064</t>
+  </si>
+  <si>
+    <t>0.6945,0.0810,0.1835,0.0045</t>
+  </si>
+  <si>
+    <t>0.6515,0.2657,0.0693,0.0018</t>
+  </si>
+  <si>
+    <t>0.9722,0.0452,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9679,0.0505,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9777,0.0336,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9490,0.0804,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.9779,0.0338,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9623,0.0616,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9876,0.0187,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9777,0.0337,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.1722,0.0349,0.7831,0.0083</t>
+  </si>
+  <si>
+    <t>0.0105,0.0067,0.9849,0.0008</t>
+  </si>
+  <si>
+    <t>0.0197,0.0389,0.9590,0.0010</t>
+  </si>
+  <si>
+    <t>0.1209,0.0542,0.8313,0.0035</t>
+  </si>
+  <si>
+    <t>0.0070,0.0125,0.9871,0.0008</t>
+  </si>
+  <si>
+    <t>0.6621,0.0307,0.3328,0.0114</t>
+  </si>
+  <si>
+    <t>0.3285,0.0866,0.5694,0.0080</t>
+  </si>
+  <si>
+    <t>0.0524,0.0053,0.9357,0.0066</t>
+  </si>
+  <si>
+    <t>0.9279,0.0739,0.0074,0.0003</t>
+  </si>
+  <si>
+    <t>0.6656,0.0490,0.1100,0.1114</t>
+  </si>
+  <si>
+    <t>0.9493,0.0069,0.0040,0.0146</t>
+  </si>
+  <si>
+    <t>0.8690,0.0052,0.0042,0.0580</t>
+  </si>
+  <si>
+    <t>0.9075,0.0416,0.0138,0.0122</t>
+  </si>
+  <si>
+    <t>0.7960,0.1499,0.0464,0.0023</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2382,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2424,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2452,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2634,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2917,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>259</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3026,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3040,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3054,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>259</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3082,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3446,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3897,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4734,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5045,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>259</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>259</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>259</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>259</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
